--- a/data/processed/harmonization/Carbon__Soil_organic_carbon/10.5440_1854940/10.5440_1854940_soil_Carbon__Soil_organic_carbon.xlsx
+++ b/data/processed/harmonization/Carbon__Soil_organic_carbon/10.5440_1854940/10.5440_1854940_soil_Carbon__Soil_organic_carbon.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="29" customWidth="1" min="7" max="7"/>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:183</t>
+          <t>TL_MM27:0-6.2:2019-08-22:183</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:172</t>
+          <t>TL_MM27:17-23.5:2019-08-22:172</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:185</t>
+          <t>TL_MM27:14.5-20.5:2019-08-22:185</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:167</t>
+          <t>TL_MM27:10-17:2019-08-22:167</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:184</t>
+          <t>TL_MM27:0-6.25:2019-08-22:184</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:181</t>
+          <t>TL_MM27:7-14.5:2019-08-22:181</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:175</t>
+          <t>TL_MM27:12-18:2019-08-23:175</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:176</t>
+          <t>TL_MM27:6-12:2019-08-23:176</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:182</t>
+          <t>TL_MM27:6.25-12.5:2019-08-23:182</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:171</t>
+          <t>TL_MM27:0-6.25:2019-08-23:171</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:163</t>
+          <t>TL_MM27:6.25-12:2019-08-23:163</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:170</t>
+          <t>TL_MM27:12-18:2019-08-23:170</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:174</t>
+          <t>TL_MM27:0-6.25:2019-08-23:174</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:189</t>
+          <t>TL_MM27:7-12:2019-08-23:189</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:188</t>
+          <t>KG_MM64:12.5-18.75:2019-08-24:188</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:186</t>
+          <t>KG_MM64:0-6.25:2019-08-24:186</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:190</t>
+          <t>KG_MM64:6.25-12.5:2019-08-24:190</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:187</t>
+          <t>KG_MM64:6.25-12.5:2019-08-24:187</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:178</t>
+          <t>KG_MM64:6.25-12.5:2019-08-24:178</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:180</t>
+          <t>KG_MM64:0-6.25:2019-08-24:180</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:192</t>
+          <t>KG_MM64:12.5-18.75:2019-08-24:192</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:140</t>
+          <t>KG_MM64:12.5-18.75:2019-08-24:140</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:date:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
